--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Relic.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Relic.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
   <si>
     <t>Key</t>
   </si>
@@ -41,12 +41,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Pricefloat</t>
-  </si>
-  <si>
     <t>Rarity</t>
   </si>
   <si>
@@ -59,6 +53,9 @@
     <t>你的子弹攻击伤害+1</t>
   </si>
   <si>
+    <t>Common</t>
+  </si>
+  <si>
     <t>Longquan Sword</t>
   </si>
   <si>
@@ -75,6 +72,9 @@
   </si>
   <si>
     <t>第30回合开始时，所有敌方单位受到无来源的30点伤害。</t>
+  </si>
+  <si>
+    <t>Rare</t>
   </si>
   <si>
     <t>Nameless Broken Sword</t>
@@ -195,7 +195,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,12 +211,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -572,7 +566,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -642,34 +636,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom style="thick">
         <color auto="1"/>
@@ -794,138 +762,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -933,72 +901,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1313,17 +1233,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="24.3" customWidth="1"/>
     <col min="2" max="2" width="23.2363636363636" customWidth="1"/>
     <col min="3" max="3" width="13.0818181818182" customWidth="1"/>
     <col min="4" max="4" width="51.5" customWidth="1"/>
-    <col min="6" max="6" width="11.2181818181818" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1339,356 +1258,260 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5">
-        <v>150</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="8" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="9">
-        <v>150</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0</v>
-      </c>
-      <c r="G3" s="11">
-        <v>1</v>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" ht="14.75" spans="1:7">
-      <c r="A4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="12" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="13">
-        <v>200</v>
-      </c>
-      <c r="F4" s="14">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15">
-        <v>2</v>
-      </c>
     </row>
-    <row r="5" ht="14.75" spans="1:7">
-      <c r="A5" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="17">
-        <v>150</v>
-      </c>
-      <c r="F5" s="18">
-        <v>0</v>
-      </c>
-      <c r="G5" s="19">
-        <v>1</v>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="5">
-        <v>150</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>1</v>
+    <row r="10" spans="1:5">
+      <c r="A10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="5">
-        <v>150</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1</v>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="9">
-        <v>200</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <v>2</v>
+    <row r="12" spans="1:5">
+      <c r="A12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="5">
-        <v>150</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7">
-        <v>1</v>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="9">
-        <v>150</v>
-      </c>
-      <c r="F10" s="10">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>1</v>
+    <row r="14" spans="1:5">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="5">
-        <v>150</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7">
-        <v>1</v>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="9">
-        <v>150</v>
-      </c>
-      <c r="F12" s="20">
-        <v>0</v>
-      </c>
-      <c r="G12" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="5">
-        <v>150</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="9">
-        <v>150</v>
-      </c>
-      <c r="F14" s="10">
-        <v>0</v>
-      </c>
-      <c r="G14" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="5">
-        <v>150</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="14.75" spans="1:7">
-      <c r="A16" s="21" t="s">
+    <row r="16" spans="1:5">
+      <c r="A16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="22">
-        <v>150</v>
-      </c>
-      <c r="F16" s="23">
-        <v>0</v>
-      </c>
-      <c r="G16" s="24">
-        <v>1</v>
+      <c r="E16" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17" ht="14.75"/>

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Relic.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Relic.xlsx
@@ -1242,7 +1242,7 @@
     <col min="4" max="4" width="51.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" ht="14.75" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" ht="14.75" spans="1:5">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" ht="14.75" spans="1:5">
       <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" ht="14.75" spans="1:5">
       <c r="A16" s="8" t="s">
         <v>49</v>
       </c>

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Relic.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Relic.xlsx
@@ -1497,7 +1497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" ht="14.75" spans="1:5">
+    <row r="16" spans="1:5">
       <c r="A16" s="8" t="s">
         <v>49</v>
       </c>

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Relic.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Relic.xlsx
@@ -1310,7 +1310,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="14.75" spans="1:5">
+    <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
